--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484535_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484535_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7021</v>
+        <v>5.0675</v>
       </c>
       <c r="E2" t="n">
-        <v>5.846</v>
+        <v>6.2857</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1439</v>
+        <v>-1.2182</v>
       </c>
       <c r="G2" t="n">
         <v>6.0646</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1401</v>
+        <v>0.2253</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6606</v>
+        <v>-0.221</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5206</v>
+        <v>0.4462</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5889</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>J. SOSA GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6699</v>
+        <v>4.5606</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4759</v>
+        <v>2.7373</v>
       </c>
       <c r="F3" t="n">
-        <v>1.194</v>
+        <v>1.8233</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5899</v>
+        <v>2.2655</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9041</v>
+        <v>3.099</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6859</v>
+        <v>-0.8335</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4743</v>
+        <v>3.2886</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3652</v>
+        <v>3.7372</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1091</v>
+        <v>-0.4486</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1157</v>
+        <v>-1.0231</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4611</v>
+        <v>-0.6382</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5768</v>
+        <v>-0.3849</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9163</v>
+        <v>2.7489</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0671</v>
+        <v>-0.1318</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4706</v>
+        <v>-0.5513</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4036</v>
+        <v>0.4195</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9034</v>
+        <v>-0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3636</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SOSA GONZALEZ</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4871</v>
+        <v>3.6743</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2426</v>
+        <v>1.2575</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2444</v>
+        <v>2.4168</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2655</v>
+        <v>2.8653</v>
       </c>
       <c r="H4" t="n">
-        <v>3.099</v>
+        <v>2.3588</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8335</v>
+        <v>0.5065</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2886</v>
+        <v>2.5709</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7372</v>
+        <v>2.5451</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4486</v>
+        <v>0.0258</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0231</v>
+        <v>0.2944</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6382</v>
+        <v>-0.1863</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3849</v>
+        <v>0.4807</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7489</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7489</v>
+        <v>2.1991</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2054</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.046</v>
+        <v>0.1686</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8406</v>
+        <v>-0.0767</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3174</v>
+        <v>3.5552</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7768</v>
+        <v>2.0886</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5406</v>
+        <v>1.4665</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8653</v>
+        <v>2.5899</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3588</v>
+        <v>1.9041</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5065</v>
+        <v>0.6859</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5709</v>
+        <v>2.4743</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5451</v>
+        <v>2.3652</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0258</v>
+        <v>0.1091</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2944</v>
+        <v>0.1157</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1863</v>
+        <v>-0.4611</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4807</v>
+        <v>0.5768</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1991</v>
+        <v>2.7489</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2651</v>
+        <v>0.9523</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3122</v>
+        <v>1.0834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0471</v>
+        <v>-0.1311</v>
       </c>
       <c r="V5" t="n">
-        <v>1.267</v>
+        <v>-0.9034</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0.3636</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6316</v>
+        <v>1.7668</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2907</v>
+        <v>0.1535</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3409</v>
+        <v>1.6134</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0155</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0.236</v>
+        <v>0.3712</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2557</v>
+        <v>0.1184</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0197</v>
+        <v>0.2528</v>
       </c>
       <c r="V6" t="n">
         <v>0.3115</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9967</v>
+        <v>0.7415</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7643</v>
+        <v>0.4348</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2324</v>
+        <v>0.3067</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1969</v>
@@ -1000,13 +1000,13 @@
         <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.3441</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3658</v>
+        <v>0.0362</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2335</v>
+        <v>0.3079</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3219</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ TEJERO</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6251</v>
+        <v>0.7201</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6251</v>
+        <v>0.6116</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.1085</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6251</v>
+        <v>1.5859</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.2585</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>0.3273</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6251</v>
+        <v>2.9355</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.5822</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>1.3533</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.3496</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.3237</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-1.0259</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.9668</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>J. MARTÍNEZ TEJERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5194</v>
+        <v>0.6251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4604</v>
+        <v>0.6251</v>
       </c>
       <c r="F9" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5859</v>
+        <v>0.6251</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2585</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3273</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9355</v>
+        <v>0.6251</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5822</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3533</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3496</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3237</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0259</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7661</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2738</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4923</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6801</v>
+        <v>-0.3282</v>
       </c>
       <c r="E10" t="n">
-        <v>0.26</v>
+        <v>0.5624</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9401</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4379</v>
@@ -1234,13 +1234,13 @@
         <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1243</v>
+        <v>0.4762</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2391</v>
+        <v>0.0634</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3633</v>
+        <v>0.4129</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0261</v>
+        <v>-0.514</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6375</v>
+        <v>-2.6177</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6114000000000001</v>
+        <v>2.1037</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1784</v>
+        <v>-2.5294</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6069</v>
+        <v>-1.8114</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7853</v>
+        <v>-0.718</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4821</v>
+        <v>-2.9917</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3993</v>
+        <v>-1.793</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8814</v>
+        <v>-1.1987</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3036</v>
+        <v>0.4623</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2075</v>
+        <v>-0.0184</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0961</v>
+        <v>0.4807</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6575</v>
+        <v>0.3661</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4389</v>
+        <v>0.3741</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2186</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0641</v>
+        <v>-1.1386</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9201</v>
+        <v>-1.7747</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8559</v>
+        <v>0.6361</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5294</v>
+        <v>-1.1784</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8114</v>
+        <v>0.6069</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.718</v>
+        <v>-1.7853</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9917</v>
+        <v>-1.4821</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.793</v>
+        <v>0.3993</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1987</v>
+        <v>-1.8814</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4623</v>
+        <v>0.3036</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0184</v>
+        <v>0.2075</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4807</v>
+        <v>0.0961</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6493</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.184</v>
+        <v>0.5451</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0717</v>
+        <v>0.3017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2557</v>
+        <v>0.2434</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1626</v>
+        <v>-1.1906</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0032</v>
+        <v>0.3467</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1657</v>
+        <v>-1.5373</v>
       </c>
       <c r="G13" t="n">
         <v>3.5891</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5049</v>
+        <v>0.4768</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2398</v>
+        <v>0.1037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7447</v>
+        <v>0.3731</v>
       </c>
       <c r="V13" t="n">
         <v>-3.7905</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9873</v>
+        <v>-3.6849</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.023</v>
+        <v>-2.7206</v>
       </c>
       <c r="F14" t="n">
         <v>-0.9643</v>
@@ -1546,10 +1546,10 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.586</v>
+        <v>-0.2836</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4774</v>
+        <v>-0.175</v>
       </c>
       <c r="U14" t="n">
         <v>-0.1086</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.0291</v>
+        <v>13.8548</v>
       </c>
       <c r="E15" t="n">
-        <v>7.164400000000001</v>
+        <v>7.990200000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8646</v>
+        <v>5.864599999999999</v>
       </c>
       <c r="G15" t="n">
         <v>15.2029</v>
@@ -1612,7 +1612,7 @@
         <v>-3.4813</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8029999999999998</v>
+        <v>-0.8029999999999996</v>
       </c>
       <c r="P15" t="n">
         <v>1.8324</v>
@@ -1624,16 +1624,16 @@
         <v>19.2421</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5746</v>
+        <v>4.4003</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9014</v>
+        <v>1.7272</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6731</v>
+        <v>2.6733</v>
       </c>
       <c r="V15" t="n">
-        <v>-7.580900000000001</v>
+        <v>-7.5809</v>
       </c>
       <c r="W15" t="n">
         <v>4.1853</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3052</v>
+        <v>4.4261</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3646</v>
+        <v>4.4607</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0594</v>
+        <v>-0.0346</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4572</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2218</v>
+        <v>-0.1009</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1297</v>
+        <v>-0.0335</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0921</v>
+        <v>-0.0673</v>
       </c>
       <c r="V16" t="n">
         <v>5.0679</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTAÑES</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5753</v>
+        <v>1.796</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5753</v>
+        <v>1.1913</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.6047</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5753</v>
+        <v>-1.5395</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3251</v>
+        <v>-0.2638</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2502</v>
+        <v>-1.2757</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5753</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3251</v>
+        <v>2.3159</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2502</v>
+        <v>-1.7882</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-2.0671</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-2.5796</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.5125</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9321</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2981</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.3597</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0616</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3823</v>
+        <v>1.5776</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0817</v>
+        <v>1.1778</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3007</v>
+        <v>0.3998</v>
       </c>
       <c r="G18" t="n">
         <v>0.4654</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8502</v>
+        <v>-0.655</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.575</v>
+        <v>-0.4759</v>
       </c>
       <c r="V18" t="n">
         <v>0.3011</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>L. SALVADOR MONTAÑES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3542</v>
+        <v>1.5753</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4341</v>
+        <v>1.5753</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9201</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1789</v>
+        <v>1.5753</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5003</v>
+        <v>0.3251</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6792</v>
+        <v>1.2502</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1575</v>
+        <v>1.5753</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9908</v>
+        <v>0.3251</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1667</v>
+        <v>1.2502</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9786</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.4911</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5125</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.733</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9321</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5864</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2979</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2885</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.355</v>
+        <v>0.3722</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2297</v>
+        <v>-0.5274</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1253</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5395</v>
+        <v>0.1789</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2638</v>
+        <v>-0.5003</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2757</v>
+        <v>0.6792</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5276999999999999</v>
+        <v>2.1575</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3159</v>
+        <v>1.9908</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7882</v>
+        <v>0.1667</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0671</v>
+        <v>-1.9786</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5796</v>
+        <v>-2.4911</v>
       </c>
       <c r="O21" t="n">
         <v>0.5125</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
         <v>2.9321</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.739</v>
+        <v>0.6045</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3212</v>
+        <v>0.3364</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4177</v>
+        <v>0.2681</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8559</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
         <v>-0.3219</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0051</v>
+        <v>-0.2574</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6969</v>
+        <v>1.1416</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6918</v>
+        <v>-1.399</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6464</v>
+        <v>-0.6624</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.3423</v>
+        <v>-0.986</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3042</v>
+        <v>0.3235</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1137</v>
+        <v>1.8106</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4145</v>
+        <v>1.1021</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5281</v>
+        <v>0.7085</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5327</v>
+        <v>-2.473</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.7567</v>
+        <v>-2.0881</v>
       </c>
       <c r="O22" t="n">
-        <v>0.224</v>
+        <v>-0.3849</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>2.9321</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8793</v>
+        <v>0.3709</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3816</v>
+        <v>-0.0746</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4977</v>
+        <v>0.4455</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5889</v>
+        <v>-0.3324</v>
       </c>
       <c r="W22" t="n">
-        <v>3.1778</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5889</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2822</v>
+        <v>-0.5631</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1416</v>
+        <v>0.12</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4238</v>
+        <v>-0.6832</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6624</v>
+        <v>-2.6464</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.986</v>
+        <v>-2.3423</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3235</v>
+        <v>-0.3042</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8106</v>
+        <v>-0.1137</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1021</v>
+        <v>0.4145</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7085</v>
+        <v>-0.5281</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.473</v>
+        <v>-2.5327</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0881</v>
+        <v>-2.7567</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3849</v>
+        <v>0.224</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2828</v>
+        <v>2.9321</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3461</v>
+        <v>0.3111</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0746</v>
+        <v>-0.1953</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4207</v>
+        <v>0.5064</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3324</v>
+        <v>1.5889</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>3.1778</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6543</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.853</v>
+        <v>-1.7043</v>
       </c>
       <c r="E24" t="n">
         <v>-1.3601</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4928</v>
+        <v>-0.3442</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0901</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5246</v>
+        <v>-0.3759</v>
       </c>
       <c r="T24" t="n">
         <v>-0.5505</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0259</v>
+        <v>0.1746</v>
       </c>
       <c r="V24" t="n">
         <v>0.3115</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2117</v>
+        <v>-2.3472</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2383</v>
+        <v>-1.5268</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9734</v>
+        <v>-0.8204</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0631</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0346</v>
+        <v>-0.1009</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2557</v>
+        <v>-0.0328</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.221</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.0292</v>
+        <v>-3.5863</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3904</v>
+        <v>-2.0057</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6388</v>
+        <v>-1.5806</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2357</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9376</v>
+        <v>-0.4947</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9359</v>
+        <v>-0.5513</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0017</v>
+        <v>0.0565</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5889</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.0891</v>
+        <v>-4.6127</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.8898</v>
+        <v>-3.7936</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1993</v>
+        <v>-0.8191000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-2.2025</v>
@@ -2560,13 +2560,13 @@
         <v>0.733</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.164</v>
+        <v>-0.6876</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6056</v>
+        <v>-0.5094</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5584</v>
+        <v>-0.1782</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6231</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.1663</v>
+        <v>-9.048299999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.1352</v>
+        <v>-6.9429</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.0312</v>
+        <v>-2.1055</v>
       </c>
       <c r="G28" t="n">
         <v>-4.1507</v>
@@ -2638,13 +2638,13 @@
         <v>0.5498</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.9839</v>
+        <v>-0.8659</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7157</v>
+        <v>-0.5234</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.2683</v>
+        <v>-0.3426</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-13.0293</v>
+        <v>-11.747</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.864799999999999</v>
+        <v>-5.864699999999997</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.1644</v>
+        <v>-5.882400000000001</v>
       </c>
       <c r="G29" t="n">
         <v>-15.2029</v>
@@ -2686,7 +2686,7 @@
         <v>-14.2407</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9624999999999999</v>
+        <v>-0.9625000000000004</v>
       </c>
       <c r="J29" t="n">
         <v>4.2843</v>
@@ -2695,7 +2695,7 @@
         <v>3.481300000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8032000000000001</v>
+        <v>0.8031999999999997</v>
       </c>
       <c r="M29" t="n">
         <v>-19.4873</v>
@@ -2707,7 +2707,7 @@
         <v>-1.7656</v>
       </c>
       <c r="P29" t="n">
-        <v>-1.8326</v>
+        <v>-1.832599999999999</v>
       </c>
       <c r="Q29" t="n">
         <v>-19.2421</v>
@@ -2716,16 +2716,16 @@
         <v>17.4094</v>
       </c>
       <c r="S29" t="n">
-        <v>-3.5747</v>
+        <v>-2.2925</v>
       </c>
       <c r="T29" t="n">
-        <v>-2.6733</v>
+        <v>-2.6732</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.9014000000000001</v>
+        <v>0.3805999999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>7.580800000000001</v>
+        <v>7.580799999999999</v>
       </c>
       <c r="W29" t="n">
         <v>11.7662</v>
